--- a/mfc_socios_to_import_FINAL16.xlsx
+++ b/mfc_socios_to_import_FINAL16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WR\madrugadores-app\carpeta 2\madrugadores-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A481DFB-4CC1-45DC-B134-68D8AAC61196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268CC65B-0501-45C7-80CC-A2B928C2C61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B8E8B8B-0AE4-4119-86C5-82C0B08C49EF}"/>
   </bookViews>
@@ -63,10 +63,10 @@
     <t>Racing</t>
   </si>
   <si>
-    <t>tafur.fredy@gmail.com</t>
-  </si>
-  <si>
-    <t>Fredy Tafur Garay</t>
+    <t xml:space="preserve">Jhody Paolo Contreras Mendo </t>
+  </si>
+  <si>
+    <t>paolocontestasmendo@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -486,13 +486,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="C2">
-        <v>41863284</v>
+        <v>42086533</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
